--- a/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-moped-ext-zugangsart.xlsx
+++ b/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-moped-ext-zugangsart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T08:52:52+00:00</t>
+    <t>2024-10-25T07:50:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-moped-ext-zugangsart.xlsx
+++ b/r5-ELGA-MOPED-186-unify-extension-nams/StructureDefinition-moped-ext-zugangsart.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:50:17+00:00</t>
+    <t>2024-10-29T09:11:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
